--- a/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/StructureDefinition-at-elga-ediag-list.xlsx
+++ b/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/StructureDefinition-at-elga-ediag-list.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T06:56:37+00:00</t>
+    <t>2026-09-09T15:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -482,7 +482,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Status des Liste.</t>
+    <t>Status der Liste.</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -512,7 +512,7 @@
     <t>List.mode</t>
   </si>
   <si>
-    <t>Die Liste wird laufend gepflegt, hat daher den fixen Wert: working.</t>
+    <t>Die Liste wird laufend gepflegt und hat daher den festen Wert: working.</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -670,8 +670,8 @@
 </t>
   </si>
   <si>
-    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. Im Falle eines GDA: eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA-Anwendung 
-des Patienten zuzugreifen. Im Falle eines Patienten: eindeutig identifiziert durch den Z-PI.</t>
+    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. Im Falle eines GDA ist sie eindeutig über den GDA-Index identifiziert und zum Zugriff auf die ELGA-Anwendung des Patienten berechtigt. 
+ Im Falle eines Patienten erfolgt die eindeutige Identifizierung über den Z-PI.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -824,7 +824,7 @@
 </t>
   </si>
   <si>
-    <t>Kennzeichnung, dass der Eintrag gelöscht wurde, ist nicht erlaubt (siehe Invariant lst-2).</t>
+    <t>Eine Kennzeichnung des Eintrags als gelöscht ist nicht zulässig (siehe Invariant list-emptyreason-required).</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -849,7 +849,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme des Eintrags in die Liste wird nicht dokumentiert, da die Liste laufend gepflegt wird und das Datum der letzten Aktualisierung der Liste (List.date) dokumentiert wird.</t>
+    <t>Das Datum der Aufnahme des Eintrags in die Liste wird nicht dokumentiert, da die Liste laufend gepflegt wird. Dokumentiert wird das Datum der letzten Aktualisierung der Liste (List.date).</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
